--- a/tests/fixtures/2025 Conflict-Related Sexual Violence (CRSV) Incident Data.xlsx
+++ b/tests/fixtures/2025 Conflict-Related Sexual Violence (CRSV) Incident Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3981" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3941" uniqueCount="561">
   <si>
     <t>Date</t>
   </si>
@@ -962,21 +962,6 @@
   </si>
   <si>
     <t>Not Applicable</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>120239</t>
@@ -2183,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="W2" s="1">
         <v>45986</v>
@@ -2251,7 +2236,7 @@
         <v>25</v>
       </c>
       <c r="V3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="W3" s="1">
         <v>45988</v>
@@ -2319,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="W4" s="1">
         <v>45960</v>
@@ -2384,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="W5" s="1">
         <v>45977</v>
@@ -2452,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="W6" s="1">
         <v>45977</v>
@@ -2520,7 +2505,7 @@
         <v>2</v>
       </c>
       <c r="V7" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="W7" s="1">
         <v>45977</v>
@@ -2588,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="W8" s="1">
         <v>45977</v>
@@ -2656,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="V9" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="W9" s="1">
         <v>45979</v>
@@ -2723,11 +2708,11 @@
       <c r="T10">
         <v>1</v>
       </c>
-      <c r="U10" t="s">
-        <v>316</v>
+      <c r="U10">
+        <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="W10" s="1">
         <v>45986</v>
@@ -2795,7 +2780,7 @@
         <v>2</v>
       </c>
       <c r="V11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="W11" s="1">
         <v>45978</v>
@@ -2863,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="W12" s="1">
         <v>45979</v>
@@ -2931,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="W13" s="1">
         <v>45985</v>
@@ -2999,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="W14" s="1">
         <v>45960</v>
@@ -3066,11 +3051,11 @@
       <c r="T15">
         <v>1</v>
       </c>
-      <c r="U15" t="s">
-        <v>316</v>
+      <c r="U15">
+        <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="W15" s="1">
         <v>45977</v>
@@ -3137,11 +3122,11 @@
       <c r="T16">
         <v>1</v>
       </c>
-      <c r="U16" t="s">
-        <v>316</v>
+      <c r="U16">
+        <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="W16" s="1">
         <v>45985</v>
@@ -3209,7 +3194,7 @@
         <v>9</v>
       </c>
       <c r="V17" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="W17" s="1">
         <v>45960</v>
@@ -3276,11 +3261,11 @@
       <c r="T18">
         <v>1</v>
       </c>
-      <c r="U18" t="s">
-        <v>316</v>
+      <c r="U18">
+        <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="W18" s="1">
         <v>45982</v>
@@ -3348,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="W19" s="1">
         <v>45982</v>
@@ -3416,7 +3401,7 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="W20" s="1">
         <v>45977</v>
@@ -3484,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="W21" s="1">
         <v>45985</v>
@@ -3552,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="W22" s="1">
         <v>45985</v>
@@ -3620,7 +3605,7 @@
         <v>4</v>
       </c>
       <c r="V23" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="W23" s="1">
         <v>45970</v>
@@ -3688,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="W24" s="1">
         <v>45976</v>
@@ -3756,7 +3741,7 @@
         <v>1</v>
       </c>
       <c r="V25" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="W25" s="1">
         <v>45976</v>
@@ -3823,11 +3808,11 @@
       <c r="T26">
         <v>1</v>
       </c>
-      <c r="U26" t="s">
-        <v>316</v>
+      <c r="U26">
+        <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="W26" s="1">
         <v>45985</v>
@@ -3895,7 +3880,7 @@
         <v>2</v>
       </c>
       <c r="V27" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="W27" s="1">
         <v>45976</v>
@@ -3962,11 +3947,11 @@
       <c r="T28">
         <v>1</v>
       </c>
-      <c r="U28" t="s">
-        <v>316</v>
+      <c r="U28">
+        <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="W28" s="1">
         <v>45977</v>
@@ -4034,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="V29" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="W29" s="1">
         <v>45976</v>
@@ -4102,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="V30" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="W30" s="1">
         <v>45979</v>
@@ -4170,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="V31" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="W31" s="1">
         <v>45985</v>
@@ -4238,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="V32" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="W32" s="1">
         <v>45977</v>
@@ -4306,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="V33" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="W33" s="1">
         <v>45970</v>
@@ -4374,7 +4359,7 @@
         <v>2</v>
       </c>
       <c r="V34" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="W34" s="1">
         <v>45979</v>
@@ -4442,7 +4427,7 @@
         <v>3</v>
       </c>
       <c r="V35" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="W35" s="1">
         <v>45979</v>
@@ -4510,7 +4495,7 @@
         <v>2</v>
       </c>
       <c r="V36" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="W36" s="1">
         <v>45976</v>
@@ -4578,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="V37" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="W37" s="1">
         <v>45976</v>
@@ -4646,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="V38" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="W38" s="1">
         <v>45958</v>
@@ -4714,7 +4699,7 @@
         <v>2</v>
       </c>
       <c r="V39" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="W39" s="1">
         <v>45979</v>
@@ -4781,11 +4766,11 @@
       <c r="T40">
         <v>2</v>
       </c>
-      <c r="U40" t="s">
-        <v>317</v>
+      <c r="U40">
+        <v>2</v>
       </c>
       <c r="V40" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="W40" s="1">
         <v>45958</v>
@@ -4853,7 +4838,7 @@
         <v>1</v>
       </c>
       <c r="V41" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="W41" s="1">
         <v>45955</v>
@@ -4921,7 +4906,7 @@
         <v>2</v>
       </c>
       <c r="V42" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="W42" s="1">
         <v>45962</v>
@@ -4988,11 +4973,11 @@
       <c r="T43">
         <v>7</v>
       </c>
-      <c r="U43" t="s">
-        <v>318</v>
+      <c r="U43">
+        <v>7</v>
       </c>
       <c r="V43" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="W43" s="1">
         <v>45955</v>
@@ -5060,7 +5045,7 @@
         <v>1</v>
       </c>
       <c r="V44" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="W44" s="1">
         <v>45957</v>
@@ -5128,7 +5113,7 @@
         <v>2</v>
       </c>
       <c r="V45" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="W45" s="1">
         <v>45960</v>
@@ -5196,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="V46" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="W46" s="1">
         <v>45977</v>
@@ -5264,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="V47" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="W47" s="1">
         <v>45958</v>
@@ -5332,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="V48" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="W48" s="1">
         <v>45958</v>
@@ -5400,7 +5385,7 @@
         <v>1</v>
       </c>
       <c r="V49" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="W49" s="1">
         <v>45954</v>
@@ -5468,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="V50" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="W50" s="1">
         <v>45967</v>
@@ -5535,11 +5520,11 @@
       <c r="T51">
         <v>5</v>
       </c>
-      <c r="U51" t="s">
-        <v>319</v>
+      <c r="U51">
+        <v>5</v>
       </c>
       <c r="V51" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="W51" s="1">
         <v>45957</v>
@@ -5607,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="V52" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="W52" s="1">
         <v>45954</v>
@@ -5675,7 +5660,7 @@
         <v>1</v>
       </c>
       <c r="V53" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="W53" s="1">
         <v>45961</v>
@@ -5743,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="V54" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="W54" s="1">
         <v>45954</v>
@@ -5811,7 +5796,7 @@
         <v>8</v>
       </c>
       <c r="V55" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="W55" s="1">
         <v>45954</v>
@@ -5879,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="V56" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="W56" s="1">
         <v>45958</v>
@@ -5947,7 +5932,7 @@
         <v>6</v>
       </c>
       <c r="V57" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="W57" s="1">
         <v>45954</v>
@@ -6015,7 +6000,7 @@
         <v>2</v>
       </c>
       <c r="V58" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="W58" s="1">
         <v>45954</v>
@@ -6082,11 +6067,11 @@
       <c r="T59">
         <v>2</v>
       </c>
-      <c r="U59" t="s">
-        <v>317</v>
+      <c r="U59">
+        <v>2</v>
       </c>
       <c r="V59" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W59" s="1">
         <v>45957</v>
@@ -6154,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="V60" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="W60" s="1">
         <v>45962</v>
@@ -6222,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="V61" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="W61" s="1">
         <v>45954</v>
@@ -6290,7 +6275,7 @@
         <v>39</v>
       </c>
       <c r="V62" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="W62" s="1">
         <v>45956</v>
@@ -6358,7 +6343,7 @@
         <v>12</v>
       </c>
       <c r="V63" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="W63" s="1">
         <v>45954</v>
@@ -6426,7 +6411,7 @@
         <v>2</v>
       </c>
       <c r="V64" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="W64" s="1">
         <v>45954</v>
@@ -6494,7 +6479,7 @@
         <v>6</v>
       </c>
       <c r="V65" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="W65" s="1">
         <v>45956</v>
@@ -6562,7 +6547,7 @@
         <v>2</v>
       </c>
       <c r="V66" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="W66" s="1">
         <v>45954</v>
@@ -6630,7 +6615,7 @@
         <v>2</v>
       </c>
       <c r="V67" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="W67" s="1">
         <v>45941</v>
@@ -6698,7 +6683,7 @@
         <v>2</v>
       </c>
       <c r="V68" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="W68" s="1">
         <v>45941</v>
@@ -6766,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="V69" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="W69" s="1">
         <v>45954</v>
@@ -6833,11 +6818,11 @@
       <c r="T70">
         <v>1</v>
       </c>
-      <c r="U70" t="s">
-        <v>316</v>
+      <c r="U70">
+        <v>1</v>
       </c>
       <c r="V70" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="W70" s="1">
         <v>45962</v>
@@ -6905,7 +6890,7 @@
         <v>1</v>
       </c>
       <c r="V71" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="W71" s="1">
         <v>45943</v>
@@ -6972,11 +6957,11 @@
       <c r="T72">
         <v>1</v>
       </c>
-      <c r="U72" t="s">
-        <v>316</v>
+      <c r="U72">
+        <v>1</v>
       </c>
       <c r="V72" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="W72" s="1">
         <v>45936</v>
@@ -7044,7 +7029,7 @@
         <v>3</v>
       </c>
       <c r="V73" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="W73" s="1">
         <v>45942</v>
@@ -7112,7 +7097,7 @@
         <v>2</v>
       </c>
       <c r="V74" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="W74" s="1">
         <v>45955</v>
@@ -7180,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="V75" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="W75" s="1">
         <v>45940</v>
@@ -7248,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="V76" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="W76" s="1">
         <v>45940</v>
@@ -7316,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="V77" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="W77" s="1">
         <v>45940</v>
@@ -7384,7 +7369,7 @@
         <v>2</v>
       </c>
       <c r="V78" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="W78" s="1">
         <v>45942</v>
@@ -7452,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="V79" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="W79" s="1">
         <v>45941</v>
@@ -7519,11 +7504,11 @@
       <c r="T80">
         <v>1</v>
       </c>
-      <c r="U80" t="s">
-        <v>316</v>
+      <c r="U80">
+        <v>1</v>
       </c>
       <c r="V80" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="W80" s="1">
         <v>45943</v>
@@ -7590,11 +7575,11 @@
       <c r="T81">
         <v>3</v>
       </c>
-      <c r="U81" t="s">
-        <v>316</v>
+      <c r="U81">
+        <v>1</v>
       </c>
       <c r="V81" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="W81" s="1">
         <v>45942</v>
@@ -7661,11 +7646,11 @@
       <c r="T82">
         <v>1</v>
       </c>
-      <c r="U82" t="s">
-        <v>316</v>
+      <c r="U82">
+        <v>1</v>
       </c>
       <c r="V82" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="W82" s="1">
         <v>45936</v>
@@ -7733,7 +7718,7 @@
         <v>1</v>
       </c>
       <c r="V83" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="W83" s="1">
         <v>45941</v>
@@ -7800,11 +7785,11 @@
       <c r="T84">
         <v>1</v>
       </c>
-      <c r="U84" t="s">
-        <v>316</v>
+      <c r="U84">
+        <v>1</v>
       </c>
       <c r="V84" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="W84" s="1">
         <v>45943</v>
@@ -7872,7 +7857,7 @@
         <v>1</v>
       </c>
       <c r="V85" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="W85" s="1">
         <v>45935</v>
@@ -7940,7 +7925,7 @@
         <v>35</v>
       </c>
       <c r="V86" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="W86" s="1">
         <v>45940</v>
@@ -8008,7 +7993,7 @@
         <v>35</v>
       </c>
       <c r="V87" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="W87" s="1">
         <v>45940</v>
@@ -8075,11 +8060,11 @@
       <c r="T88">
         <v>2</v>
       </c>
-      <c r="U88" t="s">
-        <v>317</v>
+      <c r="U88">
+        <v>2</v>
       </c>
       <c r="V88" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="W88" s="1">
         <v>45936</v>
@@ -8147,7 +8132,7 @@
         <v>1</v>
       </c>
       <c r="V89" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="W89" s="1">
         <v>45943</v>
@@ -8215,7 +8200,7 @@
         <v>8</v>
       </c>
       <c r="V90" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="W90" s="1">
         <v>45904</v>
@@ -8283,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="V91" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="W91" s="1">
         <v>45935</v>
@@ -8351,7 +8336,7 @@
         <v>11</v>
       </c>
       <c r="V92" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="W92" s="1">
         <v>45940</v>
@@ -8419,7 +8404,7 @@
         <v>1</v>
       </c>
       <c r="V93" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="W93" s="1">
         <v>45885</v>
@@ -8487,7 +8472,7 @@
         <v>15</v>
       </c>
       <c r="V94" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="W94" s="1">
         <v>45935</v>
@@ -8554,11 +8539,11 @@
       <c r="T95">
         <v>1</v>
       </c>
-      <c r="U95" t="s">
-        <v>316</v>
+      <c r="U95">
+        <v>1</v>
       </c>
       <c r="V95" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="W95" s="1">
         <v>45942</v>
@@ -8626,7 +8611,7 @@
         <v>2</v>
       </c>
       <c r="V96" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="W96" s="1">
         <v>45940</v>
@@ -8694,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="V97" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="W97" s="1">
         <v>45904</v>
@@ -8762,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="V98" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="W98" s="1">
         <v>45936</v>
@@ -8829,11 +8814,11 @@
       <c r="T99">
         <v>2</v>
       </c>
-      <c r="U99" t="s">
-        <v>317</v>
+      <c r="U99">
+        <v>2</v>
       </c>
       <c r="V99" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="W99" s="1">
         <v>45936</v>
@@ -8901,7 +8886,7 @@
         <v>1</v>
       </c>
       <c r="V100" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="W100" s="1">
         <v>45903</v>
@@ -8969,7 +8954,7 @@
         <v>1</v>
       </c>
       <c r="V101" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="W101" s="1">
         <v>45906</v>
@@ -9037,7 +9022,7 @@
         <v>1</v>
       </c>
       <c r="V102" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="W102" s="1">
         <v>45940</v>
@@ -9105,7 +9090,7 @@
         <v>2</v>
       </c>
       <c r="V103" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="W103" s="1">
         <v>45941</v>
@@ -9173,7 +9158,7 @@
         <v>12</v>
       </c>
       <c r="V104" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="W104" s="1">
         <v>45904</v>
@@ -9241,7 +9226,7 @@
         <v>2</v>
       </c>
       <c r="V105" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="W105" s="1">
         <v>45904</v>
@@ -9309,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="V106" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="W106" s="1">
         <v>45936</v>
@@ -9377,7 +9362,7 @@
         <v>2</v>
       </c>
       <c r="V107" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="W107" s="1">
         <v>45903</v>
@@ -9445,7 +9430,7 @@
         <v>74</v>
       </c>
       <c r="V108" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="W108" s="1">
         <v>45940</v>
@@ -9513,7 +9498,7 @@
         <v>4</v>
       </c>
       <c r="V109" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="W109" s="1">
         <v>45901</v>
@@ -9581,7 +9566,7 @@
         <v>2</v>
       </c>
       <c r="V110" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="W110" s="1">
         <v>45901</v>
@@ -9649,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="V111" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="W111" s="1">
         <v>45941</v>
@@ -9717,7 +9702,7 @@
         <v>1</v>
       </c>
       <c r="V112" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="W112" s="1">
         <v>45936</v>
@@ -9785,7 +9770,7 @@
         <v>2</v>
       </c>
       <c r="V113" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="W113" s="1">
         <v>45941</v>
@@ -9853,7 +9838,7 @@
         <v>3</v>
       </c>
       <c r="V114" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="W114" s="1">
         <v>45904</v>
@@ -9921,7 +9906,7 @@
         <v>1</v>
       </c>
       <c r="V115" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="W115" s="1">
         <v>45904</v>
@@ -9989,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="V116" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="W116" s="1">
         <v>45942</v>
@@ -10057,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="V117" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="W117" s="1">
         <v>45900</v>
@@ -10125,7 +10110,7 @@
         <v>1</v>
       </c>
       <c r="V118" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="W118" s="1">
         <v>45865</v>
@@ -10193,7 +10178,7 @@
         <v>95</v>
       </c>
       <c r="V119" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="W119" s="1">
         <v>45870</v>
@@ -10260,11 +10245,11 @@
       <c r="T120">
         <v>2</v>
       </c>
-      <c r="U120" t="s">
-        <v>317</v>
+      <c r="U120">
+        <v>2</v>
       </c>
       <c r="V120" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="W120" s="1">
         <v>45866</v>
@@ -10332,7 +10317,7 @@
         <v>2</v>
       </c>
       <c r="V121" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="W121" s="1">
         <v>45864</v>
@@ -10400,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="V122" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="W122" s="1">
         <v>45865</v>
@@ -10468,7 +10453,7 @@
         <v>3</v>
       </c>
       <c r="V123" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="W123" s="1">
         <v>45864</v>
@@ -10536,7 +10521,7 @@
         <v>2</v>
       </c>
       <c r="V124" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="W124" s="1">
         <v>45864</v>
@@ -10604,7 +10589,7 @@
         <v>2</v>
       </c>
       <c r="V125" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="W125" s="1">
         <v>45885</v>
@@ -10672,7 +10657,7 @@
         <v>4</v>
       </c>
       <c r="V126" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="W126" s="1">
         <v>45860</v>
@@ -10740,7 +10725,7 @@
         <v>9</v>
       </c>
       <c r="V127" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="W127" s="1">
         <v>45860</v>
@@ -10807,11 +10792,11 @@
       <c r="T128">
         <v>1</v>
       </c>
-      <c r="U128" t="s">
-        <v>316</v>
+      <c r="U128">
+        <v>1</v>
       </c>
       <c r="V128" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="W128" s="1">
         <v>45864</v>
@@ -10879,7 +10864,7 @@
         <v>1</v>
       </c>
       <c r="V129" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="W129" s="1">
         <v>45940</v>
@@ -10947,7 +10932,7 @@
         <v>8</v>
       </c>
       <c r="V130" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="W130" s="1">
         <v>45940</v>
@@ -11015,7 +11000,7 @@
         <v>5</v>
       </c>
       <c r="V131" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="W131" s="1">
         <v>45940</v>
@@ -11083,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="V132" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="W132" s="1">
         <v>45940</v>
@@ -11151,7 +11136,7 @@
         <v>1</v>
       </c>
       <c r="V133" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="W133" s="1">
         <v>45856</v>
@@ -11219,7 +11204,7 @@
         <v>2</v>
       </c>
       <c r="V134" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="W134" s="1">
         <v>45856</v>
@@ -11287,7 +11272,7 @@
         <v>2</v>
       </c>
       <c r="V135" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="W135" s="1">
         <v>45854</v>
@@ -11354,11 +11339,11 @@
       <c r="T136">
         <v>2</v>
       </c>
-      <c r="U136" t="s">
-        <v>316</v>
+      <c r="U136">
+        <v>1</v>
       </c>
       <c r="V136" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="W136" s="1">
         <v>45858</v>
@@ -11426,7 +11411,7 @@
         <v>4</v>
       </c>
       <c r="V137" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="W137" s="1">
         <v>45858</v>
@@ -11494,7 +11479,7 @@
         <v>1</v>
       </c>
       <c r="V138" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="W138" s="1">
         <v>45854</v>
@@ -11561,11 +11546,11 @@
       <c r="T139">
         <v>1</v>
       </c>
-      <c r="U139" t="s">
-        <v>316</v>
+      <c r="U139">
+        <v>1</v>
       </c>
       <c r="V139" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="W139" s="1">
         <v>45858</v>
@@ -11633,7 +11618,7 @@
         <v>2</v>
       </c>
       <c r="V140" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="W140" s="1">
         <v>45864</v>
@@ -11700,11 +11685,11 @@
       <c r="T141">
         <v>10</v>
       </c>
-      <c r="U141" t="s">
-        <v>320</v>
+      <c r="U141">
+        <v>3</v>
       </c>
       <c r="V141" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="W141" s="1">
         <v>45856</v>
@@ -11772,7 +11757,7 @@
         <v>3</v>
       </c>
       <c r="V142" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="W142" s="1">
         <v>45854</v>
@@ -11840,7 +11825,7 @@
         <v>30</v>
       </c>
       <c r="V143" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="W143" s="1">
         <v>45856</v>
@@ -11908,7 +11893,7 @@
         <v>1</v>
       </c>
       <c r="V144" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="W144" s="1">
         <v>45856</v>
@@ -11976,7 +11961,7 @@
         <v>2</v>
       </c>
       <c r="V145" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="W145" s="1">
         <v>45854</v>
@@ -12044,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="V146" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="W146" s="1">
         <v>45856</v>
@@ -12112,7 +12097,7 @@
         <v>1</v>
       </c>
       <c r="V147" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="W147" s="1">
         <v>45852</v>
@@ -12179,11 +12164,11 @@
       <c r="T148">
         <v>2</v>
       </c>
-      <c r="U148" t="s">
-        <v>317</v>
+      <c r="U148">
+        <v>2</v>
       </c>
       <c r="V148" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="W148" s="1">
         <v>45854</v>
@@ -12251,7 +12236,7 @@
         <v>1</v>
       </c>
       <c r="V149" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="W149" s="1">
         <v>45852</v>
@@ -12318,11 +12303,11 @@
       <c r="T150">
         <v>1</v>
       </c>
-      <c r="U150" t="s">
-        <v>316</v>
+      <c r="U150">
+        <v>1</v>
       </c>
       <c r="V150" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="W150" s="1">
         <v>45852</v>
@@ -12389,11 +12374,11 @@
       <c r="T151">
         <v>1</v>
       </c>
-      <c r="U151" t="s">
-        <v>316</v>
+      <c r="U151">
+        <v>1</v>
       </c>
       <c r="V151" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="W151" s="1">
         <v>45856</v>
@@ -12461,7 +12446,7 @@
         <v>2</v>
       </c>
       <c r="V152" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="W152" s="1">
         <v>45856</v>
@@ -12529,7 +12514,7 @@
         <v>2</v>
       </c>
       <c r="V153" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="W153" s="1">
         <v>45854</v>
@@ -12597,7 +12582,7 @@
         <v>5</v>
       </c>
       <c r="V154" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="W154" s="1">
         <v>45903</v>
@@ -12665,7 +12650,7 @@
         <v>1</v>
       </c>
       <c r="V155" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="W155" s="1">
         <v>45798</v>
@@ -12733,7 +12718,7 @@
         <v>1</v>
       </c>
       <c r="V156" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="W156" s="1">
         <v>45852</v>
@@ -12800,11 +12785,11 @@
       <c r="T157">
         <v>1</v>
       </c>
-      <c r="U157" t="s">
-        <v>316</v>
+      <c r="U157">
+        <v>1</v>
       </c>
       <c r="V157" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="W157" s="1">
         <v>45856</v>
@@ -12871,11 +12856,11 @@
       <c r="T158">
         <v>2</v>
       </c>
-      <c r="U158" t="s">
-        <v>317</v>
+      <c r="U158">
+        <v>2</v>
       </c>
       <c r="V158" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="W158" s="1">
         <v>45856</v>
@@ -12943,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="V159" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="W159" s="1">
         <v>45818</v>
@@ -13011,7 +12996,7 @@
         <v>4</v>
       </c>
       <c r="V160" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="W160" s="1">
         <v>45854</v>
@@ -13078,11 +13063,11 @@
       <c r="T161">
         <v>1</v>
       </c>
-      <c r="U161" t="s">
-        <v>316</v>
+      <c r="U161">
+        <v>1</v>
       </c>
       <c r="V161" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="W161" s="1">
         <v>45856</v>
@@ -13149,11 +13134,11 @@
       <c r="T162">
         <v>1</v>
       </c>
-      <c r="U162" t="s">
-        <v>316</v>
+      <c r="U162">
+        <v>1</v>
       </c>
       <c r="V162" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="W162" s="1">
         <v>45816</v>
@@ -13221,7 +13206,7 @@
         <v>1</v>
       </c>
       <c r="V163" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="W163" s="1">
         <v>45816</v>
@@ -13289,7 +13274,7 @@
         <v>3</v>
       </c>
       <c r="V164" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="W164" s="1">
         <v>45817</v>
@@ -13357,7 +13342,7 @@
         <v>2</v>
       </c>
       <c r="V165" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="W165" s="1">
         <v>45816</v>
@@ -13425,7 +13410,7 @@
         <v>1</v>
       </c>
       <c r="V166" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="W166" s="1">
         <v>45858</v>
@@ -13493,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="V167" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="W167" s="1">
         <v>45858</v>
@@ -13561,7 +13546,7 @@
         <v>1</v>
       </c>
       <c r="V168" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="W168" s="1">
         <v>45858</v>
@@ -13629,7 +13614,7 @@
         <v>2</v>
       </c>
       <c r="V169" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="W169" s="1">
         <v>45818</v>
@@ -13697,7 +13682,7 @@
         <v>5</v>
       </c>
       <c r="V170" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="W170" s="1">
         <v>45816</v>
@@ -13765,7 +13750,7 @@
         <v>1</v>
       </c>
       <c r="V171" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="W171" s="1">
         <v>45798</v>
@@ -13833,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="V172" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="W172" s="1">
         <v>45967</v>
@@ -13901,7 +13886,7 @@
         <v>8</v>
       </c>
       <c r="V173" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="W173" s="1">
         <v>45817</v>
@@ -13969,7 +13954,7 @@
         <v>1</v>
       </c>
       <c r="V174" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="W174" s="1">
         <v>45815</v>
@@ -14037,7 +14022,7 @@
         <v>72</v>
       </c>
       <c r="V175" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="W175" s="1">
         <v>45798</v>
@@ -14105,7 +14090,7 @@
         <v>1</v>
       </c>
       <c r="V176" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="W176" s="1">
         <v>45816</v>
@@ -14173,7 +14158,7 @@
         <v>1</v>
       </c>
       <c r="V177" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="W177" s="1">
         <v>45816</v>
@@ -14241,7 +14226,7 @@
         <v>2</v>
       </c>
       <c r="V178" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="W178" s="1">
         <v>45816</v>
@@ -14309,7 +14294,7 @@
         <v>2</v>
       </c>
       <c r="V179" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="W179" s="1">
         <v>45797</v>
@@ -14376,11 +14361,11 @@
       <c r="T180">
         <v>1</v>
       </c>
-      <c r="U180" t="s">
-        <v>316</v>
+      <c r="U180">
+        <v>1</v>
       </c>
       <c r="V180" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="W180" s="1">
         <v>45797</v>
@@ -14448,7 +14433,7 @@
         <v>1</v>
       </c>
       <c r="V181" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="W181" s="1">
         <v>45822</v>
@@ -14516,7 +14501,7 @@
         <v>32</v>
       </c>
       <c r="V182" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="W182" s="1">
         <v>45854</v>
@@ -14584,7 +14569,7 @@
         <v>4</v>
       </c>
       <c r="V183" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="W183" s="1">
         <v>45817</v>
@@ -14652,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="V184" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="W184" s="1">
         <v>45815</v>
@@ -14720,7 +14705,7 @@
         <v>4</v>
       </c>
       <c r="V185" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="W185" s="1">
         <v>45797</v>
@@ -14788,7 +14773,7 @@
         <v>1</v>
       </c>
       <c r="V186" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="W186" s="1">
         <v>45815</v>
@@ -14856,7 +14841,7 @@
         <v>1</v>
       </c>
       <c r="V187" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="W187" s="1">
         <v>45804</v>
@@ -14924,7 +14909,7 @@
         <v>2</v>
       </c>
       <c r="V188" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="W188" s="1">
         <v>45807</v>
@@ -14992,7 +14977,7 @@
         <v>2</v>
       </c>
       <c r="V189" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="W189" s="1">
         <v>45797</v>
@@ -15060,7 +15045,7 @@
         <v>3</v>
       </c>
       <c r="V190" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="W190" s="1">
         <v>45797</v>
@@ -15128,7 +15113,7 @@
         <v>1</v>
       </c>
       <c r="V191" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="W191" s="1">
         <v>45815</v>
@@ -15196,7 +15181,7 @@
         <v>2</v>
       </c>
       <c r="V192" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="W192" s="1">
         <v>45811</v>
@@ -15261,7 +15246,7 @@
         <v>2</v>
       </c>
       <c r="V193" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="W193" s="1">
         <v>45803</v>
@@ -15329,7 +15314,7 @@
         <v>2</v>
       </c>
       <c r="V194" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="W194" s="1">
         <v>45804</v>
@@ -15396,11 +15381,11 @@
       <c r="T195">
         <v>1</v>
       </c>
-      <c r="U195" t="s">
-        <v>316</v>
+      <c r="U195">
+        <v>1</v>
       </c>
       <c r="V195" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="W195" s="1">
         <v>45806</v>
@@ -15468,7 +15453,7 @@
         <v>1</v>
       </c>
       <c r="V196" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="W196" s="1">
         <v>45806</v>
@@ -15535,11 +15520,11 @@
       <c r="T197">
         <v>2</v>
       </c>
-      <c r="U197" t="s">
-        <v>317</v>
+      <c r="U197">
+        <v>2</v>
       </c>
       <c r="V197" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="W197" s="1">
         <v>45782</v>
@@ -15607,7 +15592,7 @@
         <v>2</v>
       </c>
       <c r="V198" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="W198" s="1">
         <v>45807</v>
@@ -15674,11 +15659,11 @@
       <c r="T199">
         <v>2</v>
       </c>
-      <c r="U199" t="s">
-        <v>317</v>
+      <c r="U199">
+        <v>2</v>
       </c>
       <c r="V199" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="W199" s="1">
         <v>45761</v>
@@ -15746,7 +15731,7 @@
         <v>2</v>
       </c>
       <c r="V200" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="W200" s="1">
         <v>45807</v>
@@ -15814,7 +15799,7 @@
         <v>2</v>
       </c>
       <c r="V201" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="W201" s="1">
         <v>45795</v>
@@ -15882,7 +15867,7 @@
         <v>1</v>
       </c>
       <c r="V202" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="W202" s="1">
         <v>45811</v>
@@ -15941,7 +15926,7 @@
         <v>1</v>
       </c>
       <c r="V203" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="W203" s="1">
         <v>45785</v>
@@ -16009,7 +15994,7 @@
         <v>5</v>
       </c>
       <c r="V204" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="W204" s="1">
         <v>45807</v>
@@ -16077,7 +16062,7 @@
         <v>2</v>
       </c>
       <c r="V205" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="W205" s="1">
         <v>45822</v>
@@ -16139,7 +16124,7 @@
         <v>3</v>
       </c>
       <c r="V206" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="W206" s="1">
         <v>45811</v>
@@ -16207,7 +16192,7 @@
         <v>1</v>
       </c>
       <c r="V207" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="W207" s="1">
         <v>45815</v>
@@ -16275,7 +16260,7 @@
         <v>1</v>
       </c>
       <c r="V208" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="W208" s="1">
         <v>45803</v>
@@ -16343,7 +16328,7 @@
         <v>2</v>
       </c>
       <c r="V209" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="W209" s="1">
         <v>45745</v>
@@ -16411,7 +16396,7 @@
         <v>1</v>
       </c>
       <c r="V210" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="W210" s="1">
         <v>45803</v>
@@ -16479,7 +16464,7 @@
         <v>1</v>
       </c>
       <c r="V211" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="W211" s="1">
         <v>45741</v>
@@ -16547,7 +16532,7 @@
         <v>4</v>
       </c>
       <c r="V212" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="W212" s="1">
         <v>45746</v>
@@ -16615,7 +16600,7 @@
         <v>6</v>
       </c>
       <c r="V213" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="W213" s="1">
         <v>45741</v>
@@ -16683,7 +16668,7 @@
         <v>2</v>
       </c>
       <c r="V214" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="W214" s="1">
         <v>45741</v>
@@ -16751,7 +16736,7 @@
         <v>1</v>
       </c>
       <c r="V215" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="W215" s="1">
         <v>45743</v>
@@ -16819,7 +16804,7 @@
         <v>1</v>
       </c>
       <c r="V216" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W216" s="1">
         <v>45806</v>
@@ -16887,7 +16872,7 @@
         <v>2</v>
       </c>
       <c r="V217" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="W217" s="1">
         <v>45744</v>
@@ -16955,7 +16940,7 @@
         <v>1</v>
       </c>
       <c r="V218" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="W218" s="1">
         <v>45744</v>
@@ -17023,7 +17008,7 @@
         <v>1</v>
       </c>
       <c r="V219" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="W219" s="1">
         <v>45744</v>
@@ -17091,7 +17076,7 @@
         <v>2</v>
       </c>
       <c r="V220" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="W220" s="1">
         <v>45744</v>
@@ -17159,7 +17144,7 @@
         <v>2</v>
       </c>
       <c r="V221" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="W221" s="1">
         <v>45795</v>
@@ -17227,7 +17212,7 @@
         <v>1</v>
       </c>
       <c r="V222" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="W222" s="1">
         <v>45744</v>
@@ -17295,7 +17280,7 @@
         <v>1</v>
       </c>
       <c r="V223" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="W223" s="1">
         <v>45744</v>
@@ -17363,7 +17348,7 @@
         <v>2</v>
       </c>
       <c r="V224" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="W224" s="1">
         <v>45744</v>
@@ -17431,7 +17416,7 @@
         <v>3</v>
       </c>
       <c r="V225" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="W225" s="1">
         <v>45753</v>
@@ -17499,7 +17484,7 @@
         <v>2</v>
       </c>
       <c r="V226" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="W226" s="1">
         <v>45741</v>
@@ -17567,7 +17552,7 @@
         <v>3</v>
       </c>
       <c r="V227" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="W227" s="1">
         <v>45792</v>
@@ -17634,11 +17619,11 @@
       <c r="T228">
         <v>2</v>
       </c>
-      <c r="U228" t="s">
-        <v>316</v>
+      <c r="U228">
+        <v>1</v>
       </c>
       <c r="V228" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="W228" s="1">
         <v>45709</v>
@@ -17706,7 +17691,7 @@
         <v>3</v>
       </c>
       <c r="V229" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="W229" s="1">
         <v>45743</v>
@@ -17773,11 +17758,11 @@
       <c r="T230">
         <v>2</v>
       </c>
-      <c r="U230" t="s">
-        <v>317</v>
+      <c r="U230">
+        <v>2</v>
       </c>
       <c r="V230" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="W230" s="1">
         <v>45743</v>
@@ -17844,11 +17829,11 @@
       <c r="T231">
         <v>1</v>
       </c>
-      <c r="U231" t="s">
-        <v>316</v>
+      <c r="U231">
+        <v>1</v>
       </c>
       <c r="V231" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="W231" s="1">
         <v>45726</v>
@@ -17916,7 +17901,7 @@
         <v>1</v>
       </c>
       <c r="V232" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="W232" s="1">
         <v>45741</v>
@@ -17984,7 +17969,7 @@
         <v>1</v>
       </c>
       <c r="V233" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="W233" s="1">
         <v>45725</v>
@@ -18052,7 +18037,7 @@
         <v>5</v>
       </c>
       <c r="V234" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="W234" s="1">
         <v>45725</v>
@@ -18119,11 +18104,11 @@
       <c r="T235">
         <v>1</v>
       </c>
-      <c r="U235" t="s">
-        <v>316</v>
+      <c r="U235">
+        <v>1</v>
       </c>
       <c r="V235" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="W235" s="1">
         <v>45726</v>
@@ -18191,7 +18176,7 @@
         <v>2</v>
       </c>
       <c r="V236" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="W236" s="1">
         <v>45727</v>
@@ -18259,7 +18244,7 @@
         <v>2</v>
       </c>
       <c r="V237" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="W237" s="1">
         <v>45822</v>
@@ -18327,7 +18312,7 @@
         <v>1</v>
       </c>
       <c r="V238" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="W238" s="1">
         <v>45700</v>
@@ -18395,7 +18380,7 @@
         <v>2</v>
       </c>
       <c r="V239" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="W239" s="1">
         <v>45725</v>
@@ -18463,7 +18448,7 @@
         <v>6</v>
       </c>
       <c r="V240" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="W240" s="1">
         <v>45726</v>
@@ -18530,11 +18515,11 @@
       <c r="T241">
         <v>1</v>
       </c>
-      <c r="U241" t="s">
-        <v>316</v>
+      <c r="U241">
+        <v>1</v>
       </c>
       <c r="V241" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="W241" s="1">
         <v>45727</v>
@@ -18602,7 +18587,7 @@
         <v>2</v>
       </c>
       <c r="V242" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="W242" s="1">
         <v>45725</v>
@@ -18670,7 +18655,7 @@
         <v>1</v>
       </c>
       <c r="V243" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="W243" s="1">
         <v>45725</v>
@@ -18738,7 +18723,7 @@
         <v>1</v>
       </c>
       <c r="V244" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="W244" s="1">
         <v>45743</v>
@@ -18806,7 +18791,7 @@
         <v>1</v>
       </c>
       <c r="V245" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="W245" s="1">
         <v>45725</v>
@@ -18874,7 +18859,7 @@
         <v>1</v>
       </c>
       <c r="V246" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="W246" s="1">
         <v>45725</v>
